--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251019_201103.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251019_201103.xlsx
@@ -5470,7 +5470,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251019_201103.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251019_201103.xlsx
@@ -5470,7 +5470,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
